--- a/www/download/COUNTRY.PRT.rpO1.xlsx
+++ b/www/download/COUNTRY.PRT.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.753131128393005</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.769213022381593</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.872996442622493</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.897054046108829</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.938262390237803</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.08271976526432</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1.11656986352008</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1.05752963778797</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.884017002857388</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.803923182519938</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.803793926327915</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.796431997418625</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.729660723050932</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.679902078434333</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948696077396</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.531</t>
+          <t>1.66582453879429</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>1.58594955871647</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.728</t>
+          <t>1.50281709146895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>1.47442189937537</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.927</t>
+          <t>1.55360372861761</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>1.50868798021721</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.121</t>
+          <t>1.42790472833294</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.151</t>
+          <t>1.47143109001522</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5.122</t>
+          <t>2.27504254827536</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.117</t>
+          <t>1.61558782214531</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.63256964180266</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.201</t>
+          <t>1.59399992140131</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5.198</t>
+          <t>1.58116190241498</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>1.57722211240466</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.053</t>
+          <t>1.55864645202877</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.576</t>
+          <t>3.40952508177977</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.618</t>
+          <t>3.28275121972692</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.724</t>
+          <t>3.16151684484268</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>3.12320400525183</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.923</t>
+          <t>3.2496478751856</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>3.16953960507233</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.07252162792308</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.121</t>
+          <t>3.1296538957426</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>4.75209497453801</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.117</t>
+          <t>3.2511348310085</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>3.3155167034741</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>3.20446061174248</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.375</t>
+          <t>3.15475676958767</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.396</t>
+          <t>3.10117296866143</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.314</t>
+          <t>3.01973192060357</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8693.292</t>
+          <t>4.20982471029841</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8720.653</t>
+          <t>4.07092470980872</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8753.428</t>
+          <t>3.88644519423826</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8907.131</t>
+          <t>3.8020526829658</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9115.373</t>
+          <t>3.99442030894116</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9296.705</t>
+          <t>3.91097193658632</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9445.794</t>
+          <t>3.78678284953603</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9496.836</t>
+          <t>3.87388149074684</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9343.179</t>
+          <t>3.30334993936635</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9429.324</t>
+          <t>3.97250777734224</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9396.913</t>
+          <t>4.02812494567278</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9539.606</t>
+          <t>3.95237372169596</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>9588.836</t>
+          <t>3.80132305229407</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>9552.777</t>
+          <t>3.66657638101008</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9196.084</t>
+          <t>3.6208612019991</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6769.189</t>
+          <t>5250171084551.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6753.915</t>
+          <t>4984116040197.72</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6802.734</t>
+          <t>4980292648344.21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6949.965</t>
+          <t>5780647013979.27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7170.217</t>
+          <t>6329079385786.39</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7306.097</t>
+          <t>7006378679487.42</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7399.159</t>
+          <t>7659909448319.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7507.101</t>
+          <t>7959849625722.16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7368.323</t>
+          <t>9109720236253.04</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7502.137</t>
+          <t>8675019770176.88</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7523.578</t>
+          <t>8083304197561.45</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7933.461</t>
+          <t>7235998233915.82</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7984.655</t>
+          <t>6215395031040.05</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7978.693</t>
+          <t>5137963845118.15</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7814.953</t>
+          <t>4284204615360.42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>978173037582.883</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>922881322558.948</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>910405116663.332</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>1070612325753.38</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>1170810076781.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>1246754684567.18</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>1362071232867.45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>1454979318288.02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>1695183262345.67</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>1592799709836.62</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>1486819499615.9</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>1363992116604.7</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>1158174774782.11</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>961969491141.803</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>883942855150.266</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>893954870.152458</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>815677799.826729</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>853597386.411894</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>951491007.869351</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1050199864.58904</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>1208674263.26186</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>1297183558.02138</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>1253257286.40123</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>1196784068.98759</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>988265068.051865</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>896488417.934127</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>745859283.936149</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>550400838.744973</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>420985265.271967</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>380899684.904125</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>127240.024482244</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>137006.514181143</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>134892.283263003</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>145203.005473805</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>149778.237068491</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>143270.008275098</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>149510.115359812</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>166052.915203629</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>201096.207212242</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>228868.284447528</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>235627.887793496</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>243111.007411007</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>275537.051519301</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>302897.525931223</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>290985.187087169</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>236030.274603288</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>251676.602704513</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>246200.548752343</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>259335.393092989</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>264672.621717817</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>258344.249673105</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>267073.474268084</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>290166.386904144</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>348926.344728717</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>399368.007892955</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>416552.592534352</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>432542.041762873</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>495471.309399575</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>545692.054806942</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>473723.136509348</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>17731.4246456308</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>18615.5934765216</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>17439.6391239375</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>18170.0777138217</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>18623.7065760445</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>18155.4086054125</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>18466.7562704419</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>20533.3261419113</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>25315.7365269341</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>28985.3787072453</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>30153.6234109167</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>34436.3887548414</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>40460.3207052331</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>55530.5518496543</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.753131128393005</t>
+          <t>273553.620891236</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769213022381593</t>
+          <t>255087.570844674</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.872996442622493</t>
+          <t>244502.515553466</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.897054046108829</t>
+          <t>278703.682447383</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262390237803</t>
+          <t>298417.208742799</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976526432</t>
+          <t>311525.120453558</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986352008</t>
+          <t>335452.475831803</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963778797</t>
+          <t>353091.448270611</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017002857388</t>
+          <t>414775.121355571</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182519938</t>
+          <t>386894.09902911</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926327915</t>
+          <t>360170.417290253</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431997418625</t>
+          <t>313072.006198289</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660723050932</t>
+          <t>264732.596429358</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902078434333</t>
+          <t>218839.636647168</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948696077396</t>
+          <t>204888.659262885</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-105963921504.374</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>-97485112424.4241</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-97737003528.1276</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>-132836530669.979</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-127043101394.006</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>-137971020457.764</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>-152423681322.538</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-149474161845.757</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>-153639671315.631</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>-158337408062.721</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>-163142192923.997</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-108719367539.139</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>-63228212338.4503</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>-110749323363.266</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-41090254899.2174</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-33703884033.2777</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>-32568133087.8421</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-32939936407.4443</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-54234478900.8741</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-66824665473.0655</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-99085908147.3674</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>-106104468391.816</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-118160945667.201</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>-132550241467.191</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>-137514725102.957</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>-138959546417.188</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>-88423943044.6208</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-53975235390.4837</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-95148144520.7701</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>-17799139671.91</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>-72260037471.0967</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>-64916979336.582</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>-64797067120.6833</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>-78602051769.1053</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>-60218435920.9404</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-38885112310.3968</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>-46319212930.7217</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>-31313216178.5562</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>-21089429848.4392</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>-20822682959.7637</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>-24182646506.809</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>-20295424494.5186</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>-9252976947.96666</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>-15601178842.4957</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23291115227.3074</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1226197.98871792</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1109499.0187493</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1036025.2279363</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1174587.81280241</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>1297258.34976535</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>1327706.39739907</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1391201.66648796</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>1485149.22177212</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>1793508.32395903</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1624460.26907876</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>1522502.68090874</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1296919.77333012</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1072299.17119844</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>864362.945998333</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>792228.940263586</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1157914.1878277</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>1086412.75409732</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1064845.69222191</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>1236780.46140556</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>1356353.43882511</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1443967.30816343</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1562550.78148714</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1646399.36492669</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1943351.46779198</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1850543.15776813</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1739335.01720491</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1553785.43676073</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1330974.60739473</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1104165.4173091</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1057044.81291544</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>166.58</t>
+          <t>27640.9337524315</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>158.59</t>
+          <t>29019.0193074826</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>150.28</t>
+          <t>28310.2427954189</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>147.44</t>
+          <t>29811.2195315843</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>155.36</t>
+          <t>29866.7838936402</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>150.87</t>
+          <t>29622.0729143587</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>142.79</t>
+          <t>29274.9031269511</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>147.14</t>
+          <t>31937.3752722009</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>227.5</t>
+          <t>39403.3919798719</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>161.56</t>
+          <t>45584.9115575512</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>163.26</t>
+          <t>46689.0464825974</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>159.4</t>
+          <t>55476.3653839372</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>158.12</t>
+          <t>66247.6968135601</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>157.72</t>
+          <t>72611.1153732561</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>155.86</t>
+          <t>56774.3546623424</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>340.95</t>
+          <t>922188023056.497</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>328.28</t>
+          <t>882856887544.736</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>316.15</t>
+          <t>898356970587.158</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>312.32</t>
+          <t>1053701593244.66</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>324.96</t>
+          <t>1140932137837.25</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>316.95</t>
+          <t>1258292904411.05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>307.25</t>
+          <t>1338336948767.69</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>312.97</t>
+          <t>1402416242646.45</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>475.21</t>
+          <t>1644730275676.23</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>325.11</t>
+          <t>1567837981314.65</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>331.55</t>
+          <t>1446216118966.52</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>320.45</t>
+          <t>1400580840516.27</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>315.48</t>
+          <t>1216495033015.44</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>310.12</t>
+          <t>1021045913380.93</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>301.97</t>
+          <t>722727462460.666</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>420.98</t>
+          <t>36177.3965766024</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>407.09</t>
+          <t>38006.2865614381</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>388.64</t>
+          <t>37903.7436388389</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>380.21</t>
+          <t>41710.3672123693</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>399.44</t>
+          <t>43418.0653201364</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>391.1</t>
+          <t>43173.7892041376</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>378.68</t>
+          <t>42744.2509021729</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>387.39</t>
+          <t>44343.7977337756</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>330.33</t>
+          <t>52010.6869567796</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>397.25</t>
+          <t>62850.1014201555</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>402.81</t>
+          <t>66279.3469024905</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>395.24</t>
+          <t>74631.9736788276</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>380.13</t>
+          <t>87100.1523424979</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>366.66</t>
+          <t>100750.894634779</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>362.09</t>
+          <t>77465.8001901647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5246277.602</t>
+          <t>1127778907313.91</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5005103.558</t>
+          <t>1077860540974.98</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5034164.495</t>
+          <t>1120425444750.9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6011000.399</t>
+          <t>1367098632919.22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6682753.393</t>
+          <t>1561051785969.76</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7263155.56</t>
+          <t>1736971610376.26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8002135.062</t>
+          <t>1845002377294.29</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8481097.049</t>
+          <t>1838217944620.22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9953846.218</t>
+          <t>2051315563067.18</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9468859.23</t>
+          <t>2038808235209.87</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8870608.588</t>
+          <t>1917874315932.78</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8081082.678</t>
+          <t>1821054518207.22</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6918252.663</t>
+          <t>1577418194533.72</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5761111.45</t>
+          <t>1333366326941.68</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5341474.863</t>
+          <t>987742693453.249</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4384638.768</t>
+          <t>-8536.46282417083</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4014056.5</t>
+          <t>-8987.26725395548</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3857639.936</t>
+          <t>-9593.50084341999</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4512061.624</t>
+          <t>-11899.1476807851</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5089663.409</t>
+          <t>-13551.2814264962</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5313613.773</t>
+          <t>-13551.7162897789</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5648835.247</t>
+          <t>-13469.3477752218</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6119834.997</t>
+          <t>-12406.4224615746</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7330057.024</t>
+          <t>-12607.2949769077</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6687721.141</t>
+          <t>-17265.1898626044</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6285043.317</t>
+          <t>-19590.3004198931</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5650420.068</t>
+          <t>-19155.6082948903</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4691186.004</t>
+          <t>-20852.4555289378</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3799543.794</t>
+          <t>-28139.7792615227</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3417881.272</t>
+          <t>-20691.4455278223</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5250171.085</t>
+          <t>-205590884257.412</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4984116.04</t>
+          <t>-195003653430.24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4980292.648</t>
+          <t>-222068474163.746</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5780647.014</t>
+          <t>-313397039674.563</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6329079.386</t>
+          <t>-420119648132.506</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7006378.679</t>
+          <t>-478678705965.21</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7659909.448</t>
+          <t>-506665428526.604</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7959849.626</t>
+          <t>-435801701973.778</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9109720.236</t>
+          <t>-406585287390.951</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8675019.77</t>
+          <t>-470970253895.218</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8083304.198</t>
+          <t>-471658196966.254</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7235998.234</t>
+          <t>-420473677690.949</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6215395.031</t>
+          <t>-360923161518.287</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5137963.845</t>
+          <t>-312320413560.754</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4284204.615</t>
+          <t>-265015230992.583</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>47261.90014</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>49497.83805</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>46463.78923</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>48461.172</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>48975.98629</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>44954.7972</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>46166.54136</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>50509.3192</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>60343.79544</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>68833.81575</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>69269.37126</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>73877.99624</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>84047.31703</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>91177.72296</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>84332.33482</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2830280.558</t>
+          <t>0.0670726849865342</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2713229.429</t>
+          <t>0.0618770037455118</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2728682.166</t>
+          <t>0.0630103284102806</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3236609.203</t>
+          <t>0.0634023739514106</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3581626.035</t>
+          <t>0.0629514694420938</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3885528.448</t>
+          <t>0.0558547872665729</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4288085.698</t>
+          <t>0.056360602009569</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4555166.603</t>
+          <t>0.0545500640497308</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5250191.669</t>
+          <t>0.0521983263470341</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4971447.019</t>
+          <t>0.0536937649049948</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4572416.373</t>
+          <t>0.0467151894374185</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4067005.402</t>
+          <t>0.040865785705064</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3456449.624</t>
+          <t>0.0467147927156727</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2851931.824</t>
+          <t>0.0268533997863547</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2631579.472</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>54517.4651070032</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>57330.1530302811</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>55091.0606983683</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>58355.0120387198</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>59941.9741107586</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>56378.2077130772</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>57660.4321514658</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>63999.5308730138</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>78562.5165176056</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>89326.0714626469</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>93752.8850865868</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>100487.676195267</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>113975.170066242</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>126619.355989369</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>119754.25756002</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>978173.038</t>
+          <t>64390.1429588036</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>922881.323</t>
+          <t>67805.5106716471</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>910405.117</t>
+          <t>64867.0389090267</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1070612.326</t>
+          <t>68669.0676641218</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1170810.077</t>
+          <t>70200.0766136047</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1246754.685</t>
+          <t>65915.005808849</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1362071.233</t>
+          <t>67564.8492680654</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1454979.318</t>
+          <t>74278.3257723271</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1695183.262</t>
+          <t>91231.3826085677</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1592799.71</t>
+          <t>103177.855088524</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1486819.5</t>
+          <t>107837.011122488</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1363992.117</t>
+          <t>113883.213810508</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1158174.775</t>
+          <t>129523.7389639</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>961969.491</t>
+          <t>143772.790474636</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>883942.855</t>
+          <t>136117.219650223</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>252503.423695737</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>265446.736551503</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>251036.482845167</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>259161.331950268</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>264984.097880274</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>256637.933778636</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>266276.129359737</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>303086.861468923</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>377851.644004267</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>441580.44506998</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>464635.182431894</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>549246.397136294</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>635663.922809273</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>748501.928456876</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>893.955</t>
+          <t>64390.1429588036</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>815.678</t>
+          <t>67480.0646625834</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>853.597</t>
+          <t>70320.8775849907</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>951.491</t>
+          <t>73474.7200641347</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1050.2</t>
+          <t>76036.5708261408</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1208.674</t>
+          <t>79078.0310994742</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1297.184</t>
+          <t>80432.0923275821</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1253.257</t>
+          <t>81181.8815101035</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1196.784</t>
+          <t>81308.8012167277</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>988.265</t>
+          <t>81803.2386717955</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>896.488</t>
+          <t>84540.4046688046</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>745.859</t>
+          <t>84545.2730358901</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>550.401</t>
+          <t>86104.4154627638</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>420.985</t>
+          <t>87777.5072634118</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>380.9</t>
+          <t>85981.5207761966</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>54517.4651070032</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>56826.1434413121</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>59341.7859978765</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>62170.0291181261</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>64303.7549449304</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>67078.8482776295</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>68071.9727332793</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>69068.4448217795</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>69126.7083017543</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>69672.5223214297</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>72063.2419286917</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>72692.9986523384</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>73652.5746550169</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>74940.7497150159</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>73062.7696026812</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>34667.5072411964</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>35040.6421883529</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>33257.5303509733</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>34601.5213958782</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>35304.8449163953</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>32489.865801151</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>33474.2392219346</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>37066.7338476729</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>45038.9599514322</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>52695.4953114758</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>51859.1439775121</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>56881.7743194917</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>70155.2290960997</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>75630.3733753642</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>69529.937939777</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4384638768057.55</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4014056499933.1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3857639936220.8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4512061624099.17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5089663409469.37</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5313613773030.83</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5648835246607.72</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6119834996949.27</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7330057023952.1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6687721140546.74</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6285043317059.37</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5650420068444.68</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4691186003734.89</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3799543794090.85</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3417881272241.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5246277602209.75</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5005103558126.36</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5034164494548.32</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6011000398523.3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6682753393091.31</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7263155560062.07</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8002135062151.95</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8481097048546.86</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9953846218030.5</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9468859229667.95</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8870608587745.03</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8081082678048.88</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6918252662566.81</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>5761111449811.42</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5341474862933.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2830280558106.89</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2713229428575.58</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2728682166053.48</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3236609203249</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3581626034899.38</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3885528447638.34</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4288085697774.46</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4555166602981.89</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5250191669245.8</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4971447019063.53</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4572416373345.79</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4067005401606.59</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3456449623603.5</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2851931823638.06</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2631579472149.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4530800</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4607000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4727600</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4860200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4927000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5030000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5121200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5151300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>5122000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5116800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>5100000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5200900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5197884.78617838</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5217616.27334019</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5053215.15007551</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3575800</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3617900</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3723500</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3841400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3923400</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4002100</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4060400</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4120686.93652677</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4086993.59017837</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4116888.09375398</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4128100</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4356800</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4374885.41420007</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4395773.57136985</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4314259.55116487</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8693291604.54445</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8720653411.22951</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8753428328.46158</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8907131147.44126</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>9115372875.80184</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9296704880.21882</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9445793656.45739</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9496836440.10518</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9343179090.48792</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9429324368.61149</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9396912528.61733</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9539605679.76632</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>9588835861.71984</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>9552776868.75569</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>9196083608.80906</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6769189057.17861</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6753915358.02492</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6802734105.03599</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6949964879.60813</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>7170217229.08824</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7306096701.79946</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7399158866.51142</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7507101468.83552</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7368322769.92465</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7502137396.7577</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7523578475.91159</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7933461390.82089</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7984655273.33706</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7978692834.63733</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7814952668.66301</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>213812.0333</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>222990.11506</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>213822.28989</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>223424.66515</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>225367.87645</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>213234.12247</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>218804.7583</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>236466.93974</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>286966.08772</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>331001.15055</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>344211.48461</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>368347.07761</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>430233.16998</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>470095.58823</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>434233.98944</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>99057.6502</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>102846.15286</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>98124.56926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>103270.58906</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>105504.92153</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>98404.87161</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>101039.08849</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>111345.05962</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>136270.34256</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>155873.3504</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>159696.1551</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>170764.98813</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>199678.96806</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>219403.16385</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>205647.15759</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>190168.190462641</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>200355.738959211</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>213535.417764474</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>229806.514114063</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>247992.67951214</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>267016.360227936</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>286126.853802035</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>302964.105787775</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>316888.833360764</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>330794.34786892</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>343547.434089003</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>358085.796585842</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>372452.561789273</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>385641.498958623</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
